--- a/checkin_frequency.xlsx
+++ b/checkin_frequency.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\0_meu_computador\0_projetos\github_repo\gymrats_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFE5E53-4074-4694-B685-6A49778E4E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE02327-D11C-4DE3-B278-ACBA1421A92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BAE092A0-8CCC-4F4F-AA4C-D35D1AC3F1E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BAE092A0-8CCC-4F4F-AA4C-D35D1AC3F1E3}"/>
   </bookViews>
   <sheets>
     <sheet name="competitors" sheetId="1" r:id="rId1"/>
@@ -1099,100 +1099,37 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <v>46180</v>
-      </c>
-      <c r="C21" s="1">
-        <v>46186</v>
-      </c>
-      <c r="D21" s="2">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2">
-        <v>5</v>
-      </c>
-      <c r="F21" s="2">
-        <v>3</v>
-      </c>
-      <c r="G21" s="2">
-        <v>5</v>
-      </c>
-      <c r="H21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0</v>
-      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <v>46187</v>
-      </c>
-      <c r="C22" s="1">
-        <v>46193</v>
-      </c>
-      <c r="D22" s="2">
-        <v>5</v>
-      </c>
-      <c r="E22" s="2">
-        <v>5</v>
-      </c>
-      <c r="F22" s="2">
-        <v>7</v>
-      </c>
-      <c r="G22" s="2">
-        <v>3</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <v>46194</v>
-      </c>
-      <c r="C23" s="1">
-        <v>46200</v>
-      </c>
-      <c r="D23" s="2">
-        <v>5</v>
-      </c>
-      <c r="E23" s="2">
-        <v>4</v>
-      </c>
-      <c r="F23" s="2">
-        <v>5</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2">
-        <v>0</v>
-      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1488,46 +1425,19 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <v>46180</v>
-      </c>
-      <c r="C21" s="1">
-        <v>46186</v>
-      </c>
-      <c r="D21" s="2">
-        <v>4</v>
-      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <v>46187</v>
-      </c>
-      <c r="C22" s="1">
-        <v>46193</v>
-      </c>
-      <c r="D22" s="2">
-        <v>4</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <v>46194</v>
-      </c>
-      <c r="C23" s="1">
-        <v>46200</v>
-      </c>
-      <c r="D23" s="2">
-        <v>4</v>
-      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/checkin_frequency.xlsx
+++ b/checkin_frequency.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\0_meu_computador\0_projetos\github_repo\gymrats_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE02327-D11C-4DE3-B278-ACBA1421A92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAF2549-57EC-47E0-B636-64790064DD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BAE092A0-8CCC-4F4F-AA4C-D35D1AC3F1E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BAE092A0-8CCC-4F4F-AA4C-D35D1AC3F1E3}"/>
   </bookViews>
   <sheets>
     <sheet name="competitors" sheetId="1" r:id="rId1"/>
@@ -1099,37 +1099,100 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46180</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D21" s="2">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2">
+        <v>5</v>
+      </c>
+      <c r="F21" s="2">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2">
+        <v>5</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46187</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D22" s="2">
+        <v>5</v>
+      </c>
+      <c r="E22" s="2">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2">
+        <v>7</v>
+      </c>
+      <c r="G22" s="2">
+        <v>3</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D23" s="2">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2">
+        <v>6</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1425,19 +1488,46 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="2"/>
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46180</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46186</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="2"/>
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46187</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46193</v>
+      </c>
+      <c r="D22" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46194</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46200</v>
+      </c>
+      <c r="D23" s="2">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
